--- a/summer_camp_surveys/039_outdoor_adventure_skills--summer_camp_surveys.xlsx
+++ b/summer_camp_surveys/039_outdoor_adventure_skills--summer_camp_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>caving</t>
+          <t>kayaking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Caving</t>
+          <t>Kayaking</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kayaking</t>
+          <t>rafting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kayaking</t>
+          <t>Rafting</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rafting</t>
+          <t>ziplining</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rafting</t>
+          <t>Ziplining</t>
         </is>
       </c>
     </row>
@@ -865,29 +865,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ziplining</t>
+          <t>zip_lining</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ziplining</t>
+          <t>Zip lining</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>adventure_skills_1_choices</t>
+          <t>adventure_skills_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>zip_lining</t>
+          <t>kayaking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zip lining</t>
+          <t>Kayaking</t>
         </is>
       </c>
     </row>
@@ -899,29 +899,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kayaking</t>
+          <t>rafting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kayaking</t>
+          <t>Rafting</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>adventure_skills_2_choices</t>
+          <t>adventure_skills_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rafting</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rafting</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hiking</t>
+          <t>cycling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hiking</t>
+          <t>Cycling</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cycling</t>
+          <t>geocaching</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Geocaching</t>
         </is>
       </c>
     </row>
@@ -967,27 +967,10 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>geocaching</t>
+          <t>orienteering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>Geocaching</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adventure_skills_3_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>orienteering</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>Orienteering</t>
         </is>
